--- a/ROUTE_4_PATH4_OLD_CANTEEN_CSE_CY_MBA_AUDI/PATH4_FINAL_ODK.xlsx
+++ b/ROUTE_4_PATH4_OLD_CANTEEN_CSE_CY_MBA_AUDI/PATH4_FINAL_ODK.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:J113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,15 +418,18 @@
         <v>required</v>
       </c>
       <c r="F1" t="str">
+        <v>required_message</v>
+      </c>
+      <c r="G1" t="str">
         <v>constraint</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>constraint_message</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>relevant</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>media::image</v>
       </c>
     </row>
@@ -438,7 +441,7 @@
         <v>start_group</v>
       </c>
       <c r="C2" t="str">
-        <v>START — TEAM INFORMATION</v>
+        <v>START — REGISTRATION</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -446,22 +449,47 @@
         <v>note</v>
       </c>
       <c r="B3" t="str">
-        <v>start_rules_note</v>
+        <v>instructions_rules_note</v>
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">🏆 FINAL CLUE — PATH 4
-### 🏴 TREASURE HUNT — RULES
-1. *No phones allowed* during the hunt. Keep them switched off and safely stored.
-2. *Stay with your team* and follow the designated route/instructions.
-3. *No cheating or interference* with other teams, clues, props, or college property.
-4. Complete all challenges *as instructed by the coordinators*. Safety comes first.
-5. Any violation of the rules may result in a *time penalty or disqualification*. The coordinator’s decision will be final.
-⚠️ IMPORTANT:
-• All questions, code entries, and photo uploads are MANDATORY.
-• All text answers and codes must be entered in UPPERCASE ONLY.</v>
+TREASURE HUNT FOR FRESHERS 2026
+Welcome to PATH 4 of the Final Clue Treasure Hunt!
+Instructions:
+Rules and Regulations:
+* Participants must report to the designated starting point 5–10 minutes before the event begins.
+* Each team must consist of 3–4 members.
+* At least one member of the team should have an Android phone.
+* Each team will receive the first clue at the beginning of the event.
+* Teams must solve each clue to find the location of the next clue.
+* Clues must be solved in the given sequence.
+* Teams are not allowed to take, hide, damage, or tamper with clues belonging to other teams.
+* Teams must remain within the designated event area.
+* Running in unsafe areas or restricted zones is prohibited.
+* Participants must not enter restricted areas or disturb ongoing events/classes.
+* Physical force, pushing, blocking, or interfering with other teams is strictly prohibited.
+* Only one device containing ODK Collect is allowed per team.
+* No use of Wi-Fi unless specifically specified. Otherwise, the team may be disqualified.
+* Participants must not damage or move any property while searching for clues.
+* Teams must follow instructions given by volunteers and organizers at all times.
+* Asking people outside the team for answers or assistance is not allowed.
+* Teams must not follow, copy, or deliberately interfere with another team's progress.
+* Tampering with clues, cheating, entering restricted areas, or intentionally misleading other teams may result in immediate disqualification.
+* The Organizing Committee will not be responsible for the loss or damage of any personal belongings of participants.
+🏆 TEAM QUALIFICATION RULES (PER PATH):
+There are 5 rounds in each path.
+From each path:
+* First 25 teams proceed to Round 2.
+* Next 15 teams proceed to Round 3.
+* Next 7 teams proceed to Round 4.
+* Next 2 teams proceed to Round 5.
+⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+• Every single question, photo upload, and code entry is strictly MANDATORY.
+• All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
+• Lowercase letters will be rejected by validation.</v>
       </c>
       <c r="D3" t="str">
-        <v>Read all rules carefully before proceeding.</v>
+        <v>Read all rules and instructions carefully.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -472,7 +500,7 @@
         <v>team_name</v>
       </c>
       <c r="C4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team Name
+        <v xml:space="preserve">Enter Team Name (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
@@ -482,9 +510,12 @@
         <v>yes</v>
       </c>
       <c r="F4" t="str">
+        <v>❌ Team Name is mandatory. Please enter in UPPERCASE.</v>
+      </c>
+      <c r="G4" t="str">
         <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>❌ Please enter Team Name in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
@@ -493,10 +524,10 @@
         <v>text</v>
       </c>
       <c r="B5" t="str">
-        <v>team_id</v>
+        <v>player_id</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team ID
+        <v xml:space="preserve">Enter Team / Player Identification (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
@@ -506,10 +537,13 @@
         <v>yes</v>
       </c>
       <c r="F5" t="str">
+        <v>❌ Player / Team ID is mandatory. Please enter in UPPERCASE.</v>
+      </c>
+      <c r="G5" t="str">
         <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
       </c>
-      <c r="G5" t="str">
-        <v>❌ Please enter Team ID in UPPERCASE (CAPS ONLY).</v>
+      <c r="H5" t="str">
+        <v>❌ Please enter Player/Team Identification in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -520,7 +554,7 @@
         <v>team_start_photo</v>
       </c>
       <c r="C6" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Team Verification Photo
+        <v xml:space="preserve">📸 Upload Team Verification Photo (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D6" t="str">
@@ -528,6 +562,9 @@
       </c>
       <c r="E6" t="str">
         <v>yes</v>
+      </c>
+      <c r="F6" t="str">
+        <v>❌ Team verification photo is strictly mandatory.</v>
       </c>
     </row>
     <row r="7">
@@ -545,8 +582,8 @@
       <c r="C8" t="str">
         <v>ROUND 1 — OBJECT FINDING</v>
       </c>
-      <c r="H8" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != ''</v>
+      <c r="I8" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != ''</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -558,15 +595,15 @@
       </c>
       <c r="C9" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 1: 🧩 OBJECT FINDING
-Challenge: Locate the assigned hidden object/code at this station.
 Instructions:
-1. Search the location to find the assigned hidden object.
-2. Take a clear photo of the object.
-3. Show the photo to the station volunteer to receive your verification code.
+1. Search the location to find the designated Cat Board physical object.
+2. Take a mandatory photo of the object.
+3. Show the object/photo to the nearby Luminus volunteer.
+4. Enter the verification code given by the volunteer.
 Enter code in caps</v>
       </c>
       <c r="D9" t="str">
-        <v>Find the assigned hidden object.</v>
+        <v>Find the Cat Board object, take photo, and ask volunteer for code.</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -577,14 +614,17 @@
         <v>r1_canteen_photo</v>
       </c>
       <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered Hidden Object
+        <v xml:space="preserve">📸 Upload Photo of Discovered Cat Board Object (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D10" t="str">
-        <v>Take a clear photo of the discovered object.</v>
+        <v>Take a clear photo of the discovered Cat Board object.</v>
       </c>
       <c r="E10" t="str">
         <v>yes</v>
+      </c>
+      <c r="F10" t="str">
+        <v>❌ Photo upload of the object is strictly mandatory.</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -595,7 +635,7 @@
         <v>r1_canteen_code</v>
       </c>
       <c r="C11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
+        <v xml:space="preserve">Enter Volunteer Verification Code (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
@@ -605,10 +645,13 @@
         <v>yes</v>
       </c>
       <c r="F11" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4'</v>
+        <v>❌ Volunteer verification code is mandatory.</v>
       </c>
       <c r="G11" t="str">
-        <v>❌ Incorrect code. Enter MEOW-BOW-4 in CAPS provided by the volunteer.</v>
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'MEOW-BOW-4'</v>
+      </c>
+      <c r="H11" t="str">
+        <v>❌ Incorrect code. Check the object again and enter the code exactly as displayed.</v>
       </c>
     </row>
     <row r="12">
@@ -626,8 +669,8 @@
       <c r="C13" t="str">
         <v>ROUND 2 LOCATION CLUE</v>
       </c>
-      <c r="H13" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != ''</v>
+      <c r="I13" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != ''</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -639,131 +682,144 @@
       </c>
       <c r="C14" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 2 LOCATION CLUE: EMOJI MATH RIDDLE
-Solve the emoji equations to calculate the destination number pointing to your next block on the station campus map!
+Solve the emoji equations below. Your final answer corresponds to a number used at the station. Use that number to identify your next location.
 🍎 + 🍎 = 10
 🍎 + 🍌 = 7
 🍌 + 🍇 = 6
-Final Equation:
+Final equation:
 🍇 + 🍎 = ?
 Enter code in caps</v>
       </c>
       <c r="D14" t="str">
-        <v>Solve the equations for the numeric value.</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
+        <v>Solve the emoji equations to find the numeric value.</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="str">
-        <v>text</v>
+        <v>integer</v>
       </c>
       <c r="B15" t="str">
         <v>r2_math_answer</v>
       </c>
-      <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter the calculated value for [ 🍇 + 🍎 ]:
-Enter code in caps</v>
+      <c r="C15" t="str">
+        <v>Enter the calculated value for [ 🍇 + 🍎 ]: (MANDATORY)</v>
       </c>
       <c r="D15" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Enter the exact integer solution.</v>
       </c>
       <c r="E15" t="str">
         <v>yes</v>
       </c>
       <c r="F15" t="str">
-        <v>normalize-space(.) = '9' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE'</v>
+        <v>❌ Solution is mandatory.</v>
       </c>
       <c r="G15" t="str">
-        <v>❌ Incorrect answer. Solve the equations to find the numeric answer.</v>
+        <v>. = 9</v>
+      </c>
+      <c r="H15" t="str">
+        <v>❌ Incorrect. Recheck the three equations and calculate the final value.</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
+        <v>note</v>
+      </c>
+      <c r="B16" t="str">
+        <v>r2_cse_proceed_note</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Go to the computational block of the campus---the house of three computing blocks, and ask the Luminus volunteer there for the START CODE.
+Enter code in caps</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Proceed to the location and ask volunteer for start code.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
         <v>text</v>
       </c>
-      <c r="B16" t="str">
-        <v>r2_cse_loc_answer</v>
-      </c>
-      <c r="C16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Which campus block does this number direct your team to on the map?
+      <c r="B17" t="str">
+        <v>r2_cse_start_code</v>
+      </c>
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
 Enter code in caps</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D17" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E16" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F16" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK'</v>
-      </c>
-      <c r="G16" t="str">
-        <v>❌ Incorrect destination. Enter the campus block name in CAPS.</v>
-      </c>
-      <c r="H16" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE')</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>end_group</v>
+      <c r="E17" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F17" t="str">
+        <v>❌ START CODE is mandatory.</v>
+      </c>
+      <c r="G17" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'CSE-START'</v>
+      </c>
+      <c r="H17" t="str">
+        <v>❌ Incorrect START CODE. Check the code at your current location and enter it exactly as provided.</v>
+      </c>
+      <c r="I17" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B18" t="str">
-        <v>cse_start_group</v>
-      </c>
-      <c r="C18" t="str">
-        <v>CSE ARRIVAL</v>
-      </c>
-      <c r="H18" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK')</v>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
-        <v>note</v>
-      </c>
       <c r="B19" t="str">
-        <v>cse_arrival_note</v>
-      </c>
-      <c r="C19" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO CSE BLOCK
-Report immediately to the CSE station and meet the volunteer to receive your CSE start code.
-Enter code in caps</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Meet volunteer at CSE station.</v>
+        <v>cse_challenge_select_group</v>
+      </c>
+      <c r="C19" t="str">
+        <v>ROUND 2 — MINI CHALLENGES</v>
+      </c>
+      <c r="I19" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START'</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>text</v>
+        <v>select_one cse_variant_list</v>
       </c>
       <c r="B20" t="str">
-        <v>r2_cse_start_code</v>
+        <v>r2_cse_variant_select</v>
       </c>
       <c r="C20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter CSE Volunteer Start Code
-Enter code in caps</v>
+        <v xml:space="preserve">Select your assigned challenge variant: (MANDATORY)
+Mandatory selection</v>
       </c>
       <c r="D20" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Choose the variant assigned by the station volunteer.</v>
       </c>
       <c r="E20" t="str">
         <v>yes</v>
       </c>
       <c r="F20" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START'</v>
-      </c>
-      <c r="G20" t="str">
-        <v>❌ Incorrect start code. Enter CSE-START in CAPS provided by the volunteer.</v>
+        <v>❌ Selecting your assigned variant is mandatory.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
+      </c>
+      <c r="B21" t="str">
+        <v>cse_v1_container</v>
+      </c>
+      <c r="C21" t="str">
+        <v>VARIANT A — LOGICAL CHALLENGE 1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>${r2_cse_variant_select} = 'var1'</v>
       </c>
     </row>
     <row r="22">
@@ -771,505 +827,645 @@
         <v>begin_group</v>
       </c>
       <c r="B22" t="str">
-        <v>cse_challenge_select_group</v>
+        <v>cse_v1_algo_group</v>
       </c>
       <c r="C22" t="str">
-        <v>ROUND 2 — CSE MINI CHALLENGES</v>
-      </c>
-      <c r="H22" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START'</v>
+        <v>CHALLENGE 1: 🏃 ALGO RELAY</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
       <c r="A23" t="str">
-        <v>select_one cse_variant_list</v>
+        <v>note</v>
       </c>
       <c r="B23" t="str">
-        <v>r2_cse_variant_select</v>
+        <v>cse_algo_intro</v>
       </c>
       <c r="C23" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select Assigned Challenge Variant
-Mandatory selection</v>
+        <v xml:space="preserve">🏃 CHALLENGE 1 — ALGO RELAY
+Answer the 10 algorithmic reasoning questions below.
+Enter code in caps</v>
       </c>
       <c r="D23" t="str">
-        <v>Choose the variant assigned by the station volunteer.</v>
-      </c>
-      <c r="E23" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>Select the correct option for each question.</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
-        <v>begin_group</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B24" t="str">
-        <v>cse_v1_container</v>
-      </c>
-      <c r="C24" t="str">
-        <v>VARIANT 1 — ALGO RELAY &amp; BINARY BREAKER</v>
+        <v>v1_algo_q1</v>
+      </c>
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q1. A program needs to calculate the average of 3 numbers. Which should happen first?
+A. Print the average
+B. Input the 3 numbers
+C. Divide by 3
+D. Add the numbers</v>
+      </c>
+      <c r="E24" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F24" t="str">
+        <v>❌ Question 1 is mandatory.</v>
+      </c>
+      <c r="G24" t="str">
+        <v>. = 'b'</v>
       </c>
       <c r="H24" t="str">
-        <v>${r2_cse_variant_select} = 'var1'</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>❌ Incorrect answer for Q1.</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
-        <v>begin_group</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B25" t="str">
-        <v>cse_v1_algo_group</v>
-      </c>
-      <c r="C25" t="str">
-        <v>CHALLENGE 1: 🏃 ALGO RELAY (10 TASKS)</v>
+        <v>v1_algo_q2</v>
+      </c>
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q2. Which is the correct order to find the largest of three numbers?
+A. Print → Input → Compare
+B. Input → Compare → Print
+C. Compare → Print → Input
+D. Print → Compare → Input</v>
+      </c>
+      <c r="E25" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F25" t="str">
+        <v>❌ Question 2 is mandatory.</v>
+      </c>
+      <c r="G25" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H25" t="str">
+        <v>❌ Incorrect answer for Q2.</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>note</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B26" t="str">
-        <v>cse_algo_intro</v>
+        <v>v1_algo_q3</v>
       </c>
       <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 ALGO RELAY — 10 TASKS
-Arrange the algorithmic steps correctly for each scenario below. Watch out for traps and fake steps!
-Enter code in caps</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Complete each algorithmic arrangement in CAPS.</v>
+        <v xml:space="preserve">Q3. What is the output?
+x = 5
+x = x + 3
+x = x × 2
+x = x - 4
+PRINT x
+A. 10
+B. 12
+C. 16
+D. 20</v>
+      </c>
+      <c r="E26" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F26" t="str">
+        <v>❌ Question 3 is mandatory.</v>
+      </c>
+      <c r="G26" t="str">
+        <v>. = 'c'</v>
+      </c>
+      <c r="H26" t="str">
+        <v>❌ Incorrect answer for Q3.</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B27" t="str">
-        <v>algo_q1</v>
+        <v>v1_algo_q4</v>
       </c>
       <c r="C27" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q1. Make Tea
-Arrange steps: Add tea powder, Boil water, Add milk, Add sugar, Strain, Serve
-Enter in caps</v>
-      </c>
-      <c r="D27" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q4. A robot starts at position 0.
++4 → -2 → +7 → -3
+Where does it finish?
+A. 4
+B. 5
+C. 6
+D. 7</v>
       </c>
       <c r="E27" t="str">
         <v>yes</v>
+      </c>
+      <c r="F27" t="str">
+        <v>❌ Question 4 is mandatory.</v>
+      </c>
+      <c r="G27" t="str">
+        <v>. = 'c'</v>
+      </c>
+      <c r="H27" t="str">
+        <v>❌ Incorrect answer for Q4.</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
       <c r="A28" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B28" t="str">
-        <v>algo_q2</v>
+        <v>v1_algo_q5</v>
       </c>
       <c r="C28" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q2. ATM Withdrawal
-Arrange: Enter PIN, Insert card, Select withdrawal, Enter amount, Collect cash, Remove card (Trap: Collect cash before amount)
-Enter in caps</v>
-      </c>
-      <c r="D28" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q5. Which condition correctly checks whether n is divisible by both 3 and 5?
+A. n % 3 == 0 OR n % 5 == 0
+B. n % 3 == 0 AND n % 5 == 0
+C. n / 3 == 0 AND n / 5 == 0
+D. n % 15 == 1</v>
       </c>
       <c r="E28" t="str">
         <v>yes</v>
+      </c>
+      <c r="F28" t="str">
+        <v>❌ Question 5 is mandatory.</v>
+      </c>
+      <c r="G28" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H28" t="str">
+        <v>❌ Incorrect answer for Q5.</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B29" t="str">
-        <v>algo_q3</v>
+        <v>v1_algo_q6</v>
       </c>
       <c r="C29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q3. Find the Largest Number
-Given 5 numbers (17, 42, 9, 63, 31), write the logic to find the largest:
-Enter in caps</v>
-      </c>
-      <c r="D29" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q6. What will this algorithm print?
+x = 10
+IF x &gt; 5
+    PRINT "A"
+ELSE
+    PRINT "B"
+A. A
+B. B
+C. A B
+D. Nothing</v>
       </c>
       <c r="E29" t="str">
         <v>yes</v>
+      </c>
+      <c r="F29" t="str">
+        <v>❌ Question 6 is mandatory.</v>
+      </c>
+      <c r="G29" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H29" t="str">
+        <v>❌ Incorrect answer for Q6.</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B30" t="str">
-        <v>algo_q4</v>
+        <v>v1_algo_q7</v>
       </c>
       <c r="C30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q4. Login System
-Arrange logic: Enter username → Enter password → Check credentials → Correct? → Allow/Deny access
-Enter in caps</v>
-      </c>
-      <c r="D30" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q7. How many times will HELLO be printed?
+FOR i = 1 TO 5
+    PRINT "HELLO"
+A. 4
+B. 5
+C. 6
+D. 10</v>
       </c>
       <c r="E30" t="str">
         <v>yes</v>
+      </c>
+      <c r="F30" t="str">
+        <v>❌ Question 7 is mandatory.</v>
+      </c>
+      <c r="G30" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H30" t="str">
+        <v>❌ Incorrect answer for Q7.</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
       <c r="A31" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B31" t="str">
-        <v>algo_q5</v>
+        <v>v1_algo_q8</v>
       </c>
       <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q5. Find a Name
-Design the steps to find whether "RAHUL" exists in a list of 100 student names:
-Enter in caps</v>
-      </c>
-      <c r="D31" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q8. What is the output?
+x = 1
+REPEAT 4 TIMES
+    x = x × 2
+PRINT x
+A. 4
+B. 8
+C. 16
+D. 32</v>
       </c>
       <c r="E31" t="str">
         <v>yes</v>
+      </c>
+      <c r="F31" t="str">
+        <v>❌ Question 8 is mandatory.</v>
+      </c>
+      <c r="G31" t="str">
+        <v>. = 'c'</v>
+      </c>
+      <c r="H31" t="str">
+        <v>❌ Incorrect answer for Q8.</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
       <c r="A32" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B32" t="str">
-        <v>algo_q6</v>
+        <v>v1_algo_q9</v>
       </c>
       <c r="C32" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q6. Odd or Even
-Create an algorithm that takes an input number and determines EVEN / ODD:
-Enter in caps</v>
-      </c>
-      <c r="D32" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q9. A sorted list is: 5, 10, 15, 20, 25, 30, 35. You want to find 30 using binary search. Which number should you check first?
+A. 5
+B. 10
+C. 20
+D. 30</v>
       </c>
       <c r="E32" t="str">
         <v>yes</v>
+      </c>
+      <c r="F32" t="str">
+        <v>❌ Question 9 is mandatory.</v>
+      </c>
+      <c r="G32" t="str">
+        <v>. = 'c'</v>
+      </c>
+      <c r="H32" t="str">
+        <v>❌ Incorrect answer for Q9.</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
       <c r="A33" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B33" t="str">
-        <v>algo_q7</v>
+        <v>v1_algo_q10</v>
       </c>
       <c r="C33" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q7. Sort Books
-Arrange the algorithm to sort 6 books of different heights from shortest → tallest:
-Enter in caps</v>
-      </c>
-      <c r="D33" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q10. You need to find a name in a sorted list of 1,000 names. Which method is generally more efficient?
+A. Check every name from the beginning
+B. Binary search
+C. Pick names randomly
+D. Check only the first name</v>
       </c>
       <c r="E33" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="34" xml:space="preserve">
+      <c r="F33" t="str">
+        <v>❌ Question 10 is mandatory.</v>
+      </c>
+      <c r="G33" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H33" t="str">
+        <v>❌ Incorrect answer for Q10.</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="str">
-        <v>text</v>
-      </c>
-      <c r="B34" t="str">
-        <v>algo_q8</v>
-      </c>
-      <c r="C34" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q8. Traffic Light Error Detection
-Identify the fake condition among: RED→STOP, YELLOW→WAIT, GREEN→GO, BLUE→GO
-Enter in caps</v>
-      </c>
-      <c r="D34" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E34" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="str">
-        <v>text</v>
+        <v>begin_group</v>
       </c>
       <c r="B35" t="str">
-        <v>algo_q9</v>
-      </c>
-      <c r="C35" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q9. Password Attempts
-Write the algorithm for 3 attempts (Correct→Login, Wrong→Retry, 3 Wrong→Locked):
-Enter in caps</v>
-      </c>
-      <c r="D35" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E35" t="str">
-        <v>yes</v>
+        <v>cse_v1_cyber_group</v>
+      </c>
+      <c r="C35" t="str">
+        <v>CHALLENGE 2: 🕵️ CYBER DETECTIVE</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
       <c r="A36" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B36" t="str">
-        <v>algo_q10</v>
+        <v>cse_cyber_intro</v>
       </c>
       <c r="C36" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q10. Final Boss: Second-Largest Number
-Write an algorithm to find the second-largest number among 10 numbers without sorting:
-Enter in caps</v>
+        <v xml:space="preserve">🕵️ CHALLENGE 2 — CYBER DETECTIVE
+Answer the 10 cyber security and detection questions below.
+Enter code in caps</v>
       </c>
       <c r="D36" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E36" t="str">
-        <v>yes</v>
+        <v>Select the correct option for each question.</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37" t="str">
-        <v>image</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B37" t="str">
-        <v>r2_v1_algo_photo</v>
+        <v>v1_cyb_q1</v>
       </c>
       <c r="C37" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Solved Algo Relay Cards
-Photo upload is mandatory</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Take a clear photo of your arranged algorithm cards.</v>
+        <v xml:space="preserve">Q1. You receive: "Your bank account will be closed today. Click this link and enter your password." What is the most likely threat?
+A. Phishing
+B. Bluetooth
+C. Backup
+D. Encryption</v>
       </c>
       <c r="E37" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="F37" t="str">
+        <v>❌ Question 1 is mandatory.</v>
+      </c>
+      <c r="G37" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H37" t="str">
+        <v>❌ Incorrect answer for Q1.</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>select_one mcq_opts</v>
+      </c>
+      <c r="B38" t="str">
+        <v>v1_cyb_q2</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q2. Which password is strongest?
+A. 12345678
+B. password123
+C. College2005
+D. R7#kP2!mQ9@x</v>
+      </c>
+      <c r="E38" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F38" t="str">
+        <v>❌ Question 2 is mandatory.</v>
+      </c>
+      <c r="G38" t="str">
+        <v>. = 'd'</v>
+      </c>
+      <c r="H38" t="str">
+        <v>❌ Incorrect answer for Q2.</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
-        <v>begin_group</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B39" t="str">
-        <v>cse_v1_binary_group</v>
-      </c>
-      <c r="C39" t="str">
-        <v>CHALLENGE 2: 🔢 BINARY BREAKER (10 QUESTIONS)</v>
+        <v>v1_cyb_q3</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q3. Someone calls pretending to be from your bank and asks for your OTP. What should you do?
+A. Give the OTP
+B. Give only half the OTP
+C. Do not share it
+D. Send your password instead</v>
+      </c>
+      <c r="E39" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F39" t="str">
+        <v>❌ Question 3 is mandatory.</v>
+      </c>
+      <c r="G39" t="str">
+        <v>. = 'c'</v>
+      </c>
+      <c r="H39" t="str">
+        <v>❌ Incorrect answer for Q3.</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str">
-        <v>note</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B40" t="str">
-        <v>cse_binary_intro</v>
+        <v>v1_cyb_q4</v>
       </c>
       <c r="C40" t="str" xml:space="preserve">
-        <v xml:space="preserve">🔢 BINARY BREAKER — 10 QUESTIONS
-Key: A=1, B=2, C=3 ... Z=26 (5-bit binary representations).
-Solve all 10 binary challenges below!
-Enter code in caps</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Answer all 10 questions in CAPS.</v>
+        <v xml:space="preserve">Q4. Which URL is most suspicious if the real website is mybank.com?
+A. mybank.com/login
+B. secure.mybank.com
+C. mybank.com
+D. mybank-login-security.com</v>
+      </c>
+      <c r="E40" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F40" t="str">
+        <v>❌ Question 4 is mandatory.</v>
+      </c>
+      <c r="G40" t="str">
+        <v>. = 'd'</v>
+      </c>
+      <c r="H40" t="str">
+        <v>❌ Incorrect answer for Q4.</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B41" t="str">
-        <v>binary_q1</v>
+        <v>v1_cyb_q5</v>
       </c>
       <c r="C41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q1. Decode: 00010 00101 00111
-Enter code in caps</v>
-      </c>
-      <c r="D41" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q5. A student uses the same password for email, Instagram and banking. What is the biggest risk?
+A. The password becomes longer
+B. One stolen password can compromise multiple accounts
+C. The internet becomes slower
+D. The phone battery drains faster</v>
       </c>
       <c r="E41" t="str">
         <v>yes</v>
       </c>
       <c r="F41" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BEG'</v>
+        <v>❌ Question 5 is mandatory.</v>
       </c>
       <c r="G41" t="str">
-        <v>❌ Incorrect. Decode using A=1 to Z=26.</v>
+        <v>. = 'b'</v>
+      </c>
+      <c r="H41" t="str">
+        <v>❌ Incorrect answer for Q5.</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B42" t="str">
-        <v>binary_q2</v>
+        <v>v1_cyb_q6</v>
       </c>
       <c r="C42" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q2. Decode: 01000 00001 00110 00110
-Enter code in caps</v>
-      </c>
-      <c r="D42" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q6. A message says: "Send this message to 20 people or your account will be deleted." What is the safest response?
+A. Forward it
+B. Send your OTP
+C. Ignore it
+D. Give the sender your password</v>
       </c>
       <c r="E42" t="str">
         <v>yes</v>
       </c>
       <c r="F42" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HALL'</v>
+        <v>❌ Question 6 is mandatory.</v>
       </c>
       <c r="G42" t="str">
-        <v>❌ Incorrect. Decode using A=1 to Z=26.</v>
+        <v>. = 'c'</v>
+      </c>
+      <c r="H42" t="str">
+        <v>❌ Incorrect answer for Q6.</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B43" t="str">
-        <v>binary_q3</v>
+        <v>v1_cyb_q7</v>
       </c>
       <c r="C43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q3. Encode "CODE" into 5-bit binary (A=1 to Z=26)
-Enter binary string (e.g. 00011 01111 00100 00101)</v>
-      </c>
-      <c r="D43" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q7. What is the main purpose of two-factor authentication?
+A. Make the screen brighter
+B. Add another layer of account security
+C. Increase internet speed
+D. Store more files</v>
       </c>
       <c r="E43" t="str">
         <v>yes</v>
       </c>
       <c r="F43" t="str">
-        <v>translate(normalize-space(.), ' ', '') = '00011011110010000101'</v>
+        <v>❌ Question 7 is mandatory.</v>
       </c>
       <c r="G43" t="str">
-        <v>❌ Incorrect. Encode C=3, O=15, D=4, E=5 in 5-bit binary.</v>
+        <v>. = 'b'</v>
+      </c>
+      <c r="H43" t="str">
+        <v>❌ Incorrect answer for Q7.</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B44" t="str">
-        <v>binary_q4</v>
+        <v>v1_cyb_q8</v>
       </c>
       <c r="C44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q4. Decimal to Binary: Convert 13 to binary
-Enter code in caps</v>
-      </c>
-      <c r="D44" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q8. A student clicks a fake login link and enters their username and password. What has most likely happened?
+A. Their credentials may have been stolen
+B. Their phone automatically upgraded
+C. Their password became stronger
+D. Their Wi-Fi was repaired</v>
       </c>
       <c r="E44" t="str">
         <v>yes</v>
       </c>
       <c r="F44" t="str">
-        <v>normalize-space(.) = '1101'</v>
+        <v>❌ Question 8 is mandatory.</v>
       </c>
       <c r="G44" t="str">
-        <v>❌ Incorrect. Convert 13 to binary.</v>
+        <v>. = 'a'</v>
+      </c>
+      <c r="H44" t="str">
+        <v>❌ Incorrect answer for Q8.</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B45" t="str">
-        <v>binary_q5</v>
+        <v>v1_cyb_q9</v>
       </c>
       <c r="C45" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q5. Binary to Decimal: Convert 10110 to decimal
-Enter code in caps</v>
-      </c>
-      <c r="D45" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q9. Which is the safest action when using a public computer?
+A. Save your password in the browser
+B. Leave your account logged in
+C. Log out after use
+D. Disable the screen lock</v>
       </c>
       <c r="E45" t="str">
         <v>yes</v>
       </c>
       <c r="F45" t="str">
-        <v>normalize-space(.) = '22'</v>
+        <v>❌ Question 9 is mandatory.</v>
       </c>
       <c r="G45" t="str">
-        <v>❌ Incorrect. Convert 10110 to decimal.</v>
+        <v>. = 'c'</v>
+      </c>
+      <c r="H45" t="str">
+        <v>❌ Incorrect answer for Q9.</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B46" t="str">
-        <v>binary_q6</v>
+        <v>v1_cyb_q10</v>
       </c>
       <c r="C46" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q6. Binary Addition: 1011 + 0110 = ?
-Enter code in caps</v>
-      </c>
-      <c r="D46" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q10. A student's account was hacked. Evidence shows: Student received a fake password-reset email, clicked the link, entered credentials, and an unknown device logged in. What is the most likely cause?
+A. Weak Wi-Fi signal
+B. Phishing
+C. Low battery
+D. Bluetooth connection</v>
       </c>
       <c r="E46" t="str">
         <v>yes</v>
       </c>
       <c r="F46" t="str">
-        <v>normalize-space(.) = '10001'</v>
+        <v>❌ Question 10 is mandatory.</v>
       </c>
       <c r="G46" t="str">
-        <v>❌ Incorrect. Perform binary addition.</v>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H46" t="str">
+        <v>❌ Incorrect answer for Q10.</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="str">
-        <v>text</v>
-      </c>
-      <c r="B47" t="str">
-        <v>binary_q7</v>
-      </c>
-      <c r="C47" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q7. Find the Odd One Out among: 00001, 00010, 00011, 00101, 00110
-Enter code in caps</v>
-      </c>
-      <c r="D47" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E47" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F47" t="str">
-        <v>normalize-space(.) = '00101'</v>
-      </c>
-      <c r="G47" t="str">
-        <v>❌ Incorrect. Look at decimal sequence 1, 2, 3, 4, 5.</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
       <c r="A48" t="str">
-        <v>text</v>
+        <v>image</v>
       </c>
       <c r="B48" t="str">
-        <v>binary_q8</v>
+        <v>r2_v1_cse_photo</v>
       </c>
       <c r="C48" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q8. ASCII Challenge: Decode 01001000 01001001 (ASCII table)
-Enter code in caps</v>
+        <v xml:space="preserve">📸 Upload Photo of Team Solving Variant 1 Challenge (MANDATORY)
+Photo upload is mandatory</v>
       </c>
       <c r="D48" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Take a clear photo of your team at the station.</v>
       </c>
       <c r="E48" t="str">
         <v>yes</v>
       </c>
       <c r="F48" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HI'</v>
-      </c>
-      <c r="G48" t="str">
-        <v>❌ Incorrect. Decode ASCII bytes 72 and 73.</v>
+        <v>❌ Station photo upload is mandatory.</v>
+      </c>
+      <c r="I48" t="str">
+        <v>${v1_algo_q1} = 'b' and ${v1_algo_q2} = 'b' and ${v1_algo_q3} = 'c' and ${v1_algo_q4} = 'c' and ${v1_algo_q5} = 'b' and ${v1_algo_q6} = 'a' and ${v1_algo_q7} = 'b' and ${v1_algo_q8} = 'c' and ${v1_algo_q9} = 'c' and ${v1_algo_q10} = 'b' and ${v1_cyb_q1} = 'a' and ${v1_cyb_q2} = 'd' and ${v1_cyb_q3} = 'c' and ${v1_cyb_q4} = 'd' and ${v1_cyb_q5} = 'b' and ${v1_cyb_q6} = 'c' and ${v1_cyb_q7} = 'b' and ${v1_cyb_q8} = 'a' and ${v1_cyb_q9} = 'c' and ${v1_cyb_q10} = 'b'</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
@@ -1277,10 +1473,10 @@
         <v>text</v>
       </c>
       <c r="B49" t="str">
-        <v>binary_q9</v>
+        <v>r2_v1_code</v>
       </c>
       <c r="C49" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q9. Binary Location: Decode 01000 00101 00001 01100 01100
+        <v xml:space="preserve">Enter Volunteer Clearance Code (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D49" t="str">
@@ -1290,543 +1486,700 @@
         <v>yes</v>
       </c>
       <c r="F49" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HEALL' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HELL'</v>
+        <v>❌ Volunteer clearance code is mandatory.</v>
       </c>
       <c r="G49" t="str">
-        <v>❌ Incorrect. Decode using A=1 to Z=26.</v>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'CSE-EINSTEIN-4'</v>
+      </c>
+      <c r="H49" t="str">
+        <v>❌ Incorrect code. Check the code obtained after completing the challenge.</v>
+      </c>
+      <c r="I49" t="str">
+        <v>${v1_algo_q1} = 'b' and ${v1_algo_q2} = 'b' and ${v1_algo_q3} = 'c' and ${v1_algo_q4} = 'c' and ${v1_algo_q5} = 'b' and ${v1_algo_q6} = 'a' and ${v1_algo_q7} = 'b' and ${v1_algo_q8} = 'c' and ${v1_algo_q9} = 'c' and ${v1_algo_q10} = 'b' and ${v1_cyb_q1} = 'a' and ${v1_cyb_q2} = 'd' and ${v1_cyb_q3} = 'c' and ${v1_cyb_q4} = 'd' and ${v1_cyb_q5} = 'b' and ${v1_cyb_q6} = 'c' and ${v1_cyb_q7} = 'b' and ${v1_cyb_q8} = 'a' and ${v1_cyb_q9} = 'c' and ${v1_cyb_q10} = 'b'</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="str">
-        <v>text</v>
-      </c>
-      <c r="B50" t="str">
-        <v>binary_q10</v>
-      </c>
-      <c r="C50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q10. Final Binary Message: Decode 01000 00001 00110 00100 01001 01010 (A=1..26)
-Enter code in caps</v>
-      </c>
-      <c r="D50" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E50" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F50" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'HAFDIJ' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'IBGEJK'</v>
-      </c>
-      <c r="G50" t="str">
-        <v>❌ Incorrect. Decode the 6 letters using A=1 to Z=26.</v>
-      </c>
-    </row>
-    <row r="51" xml:space="preserve">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="str">
-        <v>image</v>
+        <v>begin_group</v>
       </c>
       <c r="B51" t="str">
-        <v>r2_v1_binary_photo</v>
-      </c>
-      <c r="C51" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Team Solving Binary Breaker
-Photo upload is mandatory</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Take a clear photo of your team solving Binary Breaker.</v>
-      </c>
-      <c r="E51" t="str">
-        <v>yes</v>
+        <v>cse_v2_container</v>
+      </c>
+      <c r="C51" t="str">
+        <v>VARIANT B — LOGICAL CHALLENGE 2</v>
+      </c>
+      <c r="I51" t="str">
+        <v>${r2_cse_variant_select} = 'var2'</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
+      </c>
+      <c r="B52" t="str">
+        <v>cse_v2_bug_group</v>
+      </c>
+      <c r="C52" t="str">
+        <v>CHALLENGE 3: 🐛 BUG HUNTER</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
       <c r="A53" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B53" t="str">
-        <v>r2_v1_code</v>
+        <v>cse_bug_intro</v>
       </c>
       <c r="C53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code (Variant 1)
+        <v xml:space="preserve">🐛 CHALLENGE 3 — BUG HUNTER
+Find the bug in each of the 10 code snippets below.
 Enter code in caps</v>
       </c>
       <c r="D53" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E53" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F53" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4'</v>
-      </c>
-      <c r="G53" t="str">
-        <v>❌ Incorrect code. Enter CSE-EINSTEIN-4 provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>Select the correct option for each question.</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>select_one mcq_opts</v>
+      </c>
+      <c r="B54" t="str">
+        <v>v2_bug_q1</v>
+      </c>
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q1. What is wrong with this program?
+IF age &gt; 18
+    PRINT "ELIGIBLE"
+ELSE
+    PRINT "NOT ELIGIBLE"
+A person who is exactly 18 is being rejected. What should change?
+A. &gt; to &gt;=
+B. &gt; to &lt;
+C. 18 to 19
+D. Remove ELSE</v>
+      </c>
+      <c r="E54" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F54" t="str">
+        <v>❌ Question 1 is mandatory.</v>
+      </c>
+      <c r="G54" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H54" t="str">
+        <v>❌ Incorrect answer for Q1.</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
       <c r="A55" t="str">
-        <v>begin_group</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B55" t="str">
-        <v>cse_v2_container</v>
-      </c>
-      <c r="C55" t="str">
-        <v>VARIANT 2 — PATTERN HACK &amp; BUG HUNTER</v>
+        <v>v2_bug_q2</v>
+      </c>
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q2. What will this program print?
+x = 2
+WHILE x &lt; 10
+    PRINT x
+    x = x + 2
+A. 2 4 6 8
+B. 2 4 6 8 10
+C. 1 2 3 4
+D. Infinite loop</v>
+      </c>
+      <c r="E55" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F55" t="str">
+        <v>❌ Question 2 is mandatory.</v>
+      </c>
+      <c r="G55" t="str">
+        <v>. = 'a'</v>
       </c>
       <c r="H55" t="str">
-        <v>${r2_cse_variant_select} = 'var2'</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>❌ Incorrect answer for Q2.</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
-        <v>begin_group</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B56" t="str">
-        <v>cse_v2_pattern_group</v>
-      </c>
-      <c r="C56" t="str">
-        <v>CHALLENGE 1: 🧠 PATTERN HACK (10 QUESTIONS)</v>
+        <v>v2_bug_q3</v>
+      </c>
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q3. What is the bug?
+IF marks &gt;= 40
+    PRINT "FAIL"
+ELSE
+    PRINT "PASS"
+A. &gt;= should be &lt;=
+B. PASS and FAIL are reversed
+C. Marks cannot be compared
+D. ELSE must be removed</v>
+      </c>
+      <c r="E56" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F56" t="str">
+        <v>❌ Question 3 is mandatory.</v>
+      </c>
+      <c r="G56" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H56" t="str">
+        <v>❌ Incorrect answer for Q3.</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
       <c r="A57" t="str">
-        <v>note</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B57" t="str">
-        <v>cse_pattern_intro</v>
+        <v>v2_bug_q4</v>
       </c>
       <c r="C57" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧠 PATTERN HACK — 10 QUESTIONS
-Find the missing number, letter, or rule for each sequence below!
-Enter code in caps</v>
-      </c>
-      <c r="D57" t="str">
-        <v>Answer all 10 questions in CAPS.</v>
+        <v xml:space="preserve">Q4. What will be the output?
+a = 5
+b = 3
+a = a + b
+b = a - b
+a = a - b
+PRINT a
+PRINT b
+A. 5 3
+B. 3 5
+C. 8 3
+D. 8 5</v>
+      </c>
+      <c r="E57" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F57" t="str">
+        <v>❌ Question 4 is mandatory.</v>
+      </c>
+      <c r="G57" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H57" t="str">
+        <v>❌ Incorrect answer for Q4.</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
       <c r="A58" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B58" t="str">
-        <v>pattern_q1</v>
+        <v>v2_bug_q5</v>
       </c>
       <c r="C58" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q1. Find next: 2, 4, 6, 8, ?
-Enter code in caps</v>
-      </c>
-      <c r="D58" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q5. A program should print numbers from 1 to 5.
+i = 1
+WHILE i &lt;= 5
+    PRINT i
+What is missing?
+A. i = i + 1
+B. i = i - 1
+C. i = 0
+D. PRINT i</v>
       </c>
       <c r="E58" t="str">
         <v>yes</v>
       </c>
       <c r="F58" t="str">
-        <v>normalize-space(.) = '10'</v>
+        <v>❌ Question 5 is mandatory.</v>
       </c>
       <c r="G58" t="str">
-        <v>❌ Incorrect answer.</v>
+        <v>. = 'a'</v>
+      </c>
+      <c r="H58" t="str">
+        <v>❌ Incorrect answer for Q5.</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
       <c r="A59" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B59" t="str">
-        <v>pattern_q2</v>
+        <v>v2_bug_q6</v>
       </c>
       <c r="C59" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q2. Find next: 3, 6, 12, 24, ?
-Enter code in caps</v>
-      </c>
-      <c r="D59" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q6. A program checks whether a number is positive:
+IF number &gt; 0
+    PRINT "POSITIVE"
+ELSE
+    PRINT "NEGATIVE"
+What happens when the input is 0?
+A. POSITIVE
+B. NEGATIVE
+C. Neither is mathematically correct
+D. It always prints both</v>
       </c>
       <c r="E59" t="str">
         <v>yes</v>
       </c>
       <c r="F59" t="str">
-        <v>normalize-space(.) = '48'</v>
+        <v>❌ Question 6 is mandatory.</v>
       </c>
       <c r="G59" t="str">
-        <v>❌ Incorrect answer.</v>
+        <v>. = 'b'</v>
+      </c>
+      <c r="H59" t="str">
+        <v>❌ Incorrect answer for Q6.</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B60" t="str">
-        <v>pattern_q3</v>
+        <v>v2_bug_q7</v>
       </c>
       <c r="C60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q3. Find next: 1, 4, 9, 16, 25, ?
-Enter code in caps</v>
-      </c>
-      <c r="D60" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q7. A calculator produces: 8 × 0 = 8. What is the bug?
+A. Multiplication is incorrect
+B. Addition is incorrect
+C. Division is incorrect
+D. Nothing is wrong</v>
       </c>
       <c r="E60" t="str">
         <v>yes</v>
       </c>
       <c r="F60" t="str">
-        <v>normalize-space(.) = '36'</v>
+        <v>❌ Question 7 is mandatory.</v>
       </c>
       <c r="G60" t="str">
-        <v>❌ Incorrect answer.</v>
+        <v>. = 'a'</v>
+      </c>
+      <c r="H60" t="str">
+        <v>❌ Incorrect answer for Q7.</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
       <c r="A61" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B61" t="str">
-        <v>pattern_q4</v>
+        <v>v2_bug_q8</v>
       </c>
       <c r="C61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q4. Find next: 1, 1, 2, 3, 5, 8, ?
-Enter code in caps</v>
-      </c>
-      <c r="D61" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q8. A program should calculate: 10 + 20 × 2. The programmer calculates: (10 + 20) × 2 = 60. What rule was ignored?
+A. Multiplication has priority over addition
+B. Addition has priority over multiplication
+C. Division must happen first
+D. Subtraction must happen first</v>
       </c>
       <c r="E61" t="str">
         <v>yes</v>
       </c>
       <c r="F61" t="str">
-        <v>normalize-space(.) = '13'</v>
+        <v>❌ Question 8 is mandatory.</v>
       </c>
       <c r="G61" t="str">
-        <v>❌ Incorrect answer.</v>
+        <v>. = 'a'</v>
+      </c>
+      <c r="H61" t="str">
+        <v>❌ Incorrect answer for Q8.</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
       <c r="A62" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B62" t="str">
-        <v>pattern_q5</v>
+        <v>v2_bug_q9</v>
       </c>
       <c r="C62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q5. Find next: A, C, F, J, O, ?
-Enter code in caps</v>
-      </c>
-      <c r="D62" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q9. A program is supposed to find the largest number.
+largest = 0
+IF number &lt; largest
+    largest = number
+What is the main problem?
+A. It updates when a smaller number is found
+B. It updates when a larger number is found
+C. largest should always be 100
+D. There is no comparison</v>
       </c>
       <c r="E62" t="str">
         <v>yes</v>
       </c>
       <c r="F62" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'U'</v>
+        <v>❌ Question 9 is mandatory.</v>
       </c>
       <c r="G62" t="str">
-        <v>❌ Incorrect answer. Follow letter positions +2, +3, +4, +5, +6.</v>
+        <v>. = 'a'</v>
+      </c>
+      <c r="H62" t="str">
+        <v>❌ Incorrect answer for Q9.</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
       <c r="A63" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B63" t="str">
-        <v>pattern_q6</v>
+        <v>v2_bug_q10</v>
       </c>
       <c r="C63" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q6. Rule: 2→6, 3→12, 4→20, 5→30, 6→?
-Enter code in caps</v>
-      </c>
-      <c r="D63" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q10. A discount should be given only when: Amount ≥ ₹1,000 AND customer is a member.
+The programmer writes:
+IF amount &gt;= 1000 OR member == YES
+    PRINT "DISCOUNT"
+What is the bug?
+A. OR should be AND
+B. AND should be OR
+C. Amount should be ₹100
+D. Member status should be ignored</v>
       </c>
       <c r="E63" t="str">
         <v>yes</v>
       </c>
       <c r="F63" t="str">
-        <v>normalize-space(.) = '42'</v>
+        <v>❌ Question 10 is mandatory.</v>
       </c>
       <c r="G63" t="str">
-        <v>❌ Incorrect answer. Follow n * (n+1).</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H63" t="str">
+        <v>❌ Incorrect answer for Q10.</v>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" t="str">
-        <v>text</v>
-      </c>
-      <c r="B64" t="str">
-        <v>pattern_q7</v>
-      </c>
-      <c r="C64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q7. What comes next: 1A, 2B, 4D, 8H, 16P, ?
-Enter code in caps</v>
-      </c>
-      <c r="D64" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E64" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F64" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '32F'</v>
-      </c>
-      <c r="G64" t="str">
-        <v>❌ Incorrect answer. Numbers double, letters double modulo 26.</v>
-      </c>
-    </row>
-    <row r="65" xml:space="preserve">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65" t="str">
-        <v>text</v>
+        <v>begin_group</v>
       </c>
       <c r="B65" t="str">
-        <v>pattern_q8</v>
-      </c>
-      <c r="C65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q8. Find missing: 2, 3, 5, 9, 17, ?
-Enter code in caps</v>
-      </c>
-      <c r="D65" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E65" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F65" t="str">
-        <v>normalize-space(.) = '33'</v>
-      </c>
-      <c r="G65" t="str">
-        <v>❌ Incorrect answer. Rule: *2 - 1.</v>
+        <v>cse_v2_tech_group</v>
+      </c>
+      <c r="C65" t="str">
+        <v>CHALLENGE 4: 💻 TECH DETECTIVE</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B66" t="str">
-        <v>pattern_q9</v>
+        <v>cse_tech_intro</v>
       </c>
       <c r="C66" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q9. Visual Logic: If ★=10, ▲=3, ■=4. Calculate [ ★ + ▲ × ■ ]:
+        <v xml:space="preserve">💻 CHALLENGE 4 — TECH DETECTIVE
+Answer the 10 technology and networking questions below.
 Enter code in caps</v>
       </c>
       <c r="D66" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E66" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F66" t="str">
-        <v>normalize-space(.) = '22'</v>
-      </c>
-      <c r="G66" t="str">
-        <v>❌ Incorrect answer. Remember operator precedence (* before +).</v>
+        <v>Select the correct option for each question.</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
       <c r="A67" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B67" t="str">
-        <v>pattern_q10</v>
+        <v>v2_tech_q1</v>
       </c>
       <c r="C67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q10. What does the series 1, 2, 4, 8, 16 represent?
-Enter code in caps</v>
-      </c>
-      <c r="D67" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q1. Which device connects different networks and directs data between them?
+A. Monitor
+B. Router
+C. Keyboard
+D. Printer</v>
       </c>
       <c r="E67" t="str">
         <v>yes</v>
       </c>
       <c r="F67" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'POWERS OF 2' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'POWER OF 2' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'POWERS OF TWO' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BINARY'</v>
+        <v>❌ Question 1 is mandatory.</v>
       </c>
       <c r="G67" t="str">
-        <v>❌ Incorrect answer. Think about powers in computing.</v>
+        <v>. = 'b'</v>
+      </c>
+      <c r="H67" t="str">
+        <v>❌ Incorrect answer for Q1.</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
       <c r="A68" t="str">
-        <v>image</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B68" t="str">
-        <v>r2_v2_pattern_photo</v>
+        <v>v2_tech_q2</v>
       </c>
       <c r="C68" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Team Solving Pattern Hack
-Photo upload is mandatory</v>
-      </c>
-      <c r="D68" t="str">
-        <v>Take a clear photo of your team solving Pattern Hack.</v>
+        <v xml:space="preserve">Q2. You type: www.example.com. Which system finds the IP address associated with this domain?
+A. DNS
+B. USB
+C. HDMI
+D. RAM</v>
       </c>
       <c r="E68" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="69">
+      <c r="F68" t="str">
+        <v>❌ Question 2 is mandatory.</v>
+      </c>
+      <c r="G68" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H68" t="str">
+        <v>❌ Incorrect answer for Q2.</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
       <c r="A69" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>select_one mcq_opts</v>
+      </c>
+      <c r="B69" t="str">
+        <v>v2_tech_q3</v>
+      </c>
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q3. Which of these is an operating system?
+A. Chrome
+B. Windows
+C. YouTube
+D. Google</v>
+      </c>
+      <c r="E69" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F69" t="str">
+        <v>❌ Question 3 is mandatory.</v>
+      </c>
+      <c r="G69" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H69" t="str">
+        <v>❌ Incorrect answer for Q3.</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
       <c r="A70" t="str">
-        <v>begin_group</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B70" t="str">
-        <v>cse_v2_bug_group</v>
-      </c>
-      <c r="C70" t="str">
-        <v>CHALLENGE 2: 🐛 BUG HUNTER (DEBUG THE SYSTEM)</v>
+        <v>v2_tech_q4</v>
+      </c>
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Q4. Which statement about RAM is correct?
+A. It is mainly used as temporary working memory
+B. It permanently stores files even without power
+C. It is used only for printing
+D. It is the same as a keyboard</v>
+      </c>
+      <c r="E70" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F70" t="str">
+        <v>❌ Question 4 is mandatory.</v>
+      </c>
+      <c r="G70" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H70" t="str">
+        <v>❌ Incorrect answer for Q4.</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
       <c r="A71" t="str">
-        <v>note</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B71" t="str">
-        <v>cse_bug_intro</v>
+        <v>v2_tech_q5</v>
       </c>
       <c r="C71" t="str" xml:space="preserve">
-        <v xml:space="preserve">🐛 BUG HUNTER — DEBUG THE SYSTEM
-Examine the programs, pseudocode, and flowcharts below. Find the logic and syntax bugs!
-Enter code in caps</v>
-      </c>
-      <c r="D71" t="str">
-        <v>Identify and describe the bugs in CAPS.</v>
+        <v xml:space="preserve">Q5. Which protocol is used for secure web browsing?
+A. HTTP
+B. HTTPS
+C. FTP
+D. SMTP</v>
+      </c>
+      <c r="E71" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F71" t="str">
+        <v>❌ Question 5 is mandatory.</v>
+      </c>
+      <c r="G71" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H71" t="str">
+        <v>❌ Incorrect answer for Q5.</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
       <c r="A72" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B72" t="str">
-        <v>bug_q1</v>
+        <v>v2_tech_q6</v>
       </c>
       <c r="C72" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q1. Output Bug: x=10, y=20. IF x&gt;y PRINT "10 is greater" ELSE PRINT "20 is greater". What is wrong?
-Enter in caps</v>
-      </c>
-      <c r="D72" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q6. A device automatically receives an IP address when joining a network. Which service commonly provides it?
+A. DNS
+B. DHCP
+C. HTTP
+D. HTML</v>
       </c>
       <c r="E72" t="str">
         <v>yes</v>
+      </c>
+      <c r="F72" t="str">
+        <v>❌ Question 6 is mandatory.</v>
+      </c>
+      <c r="G72" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H72" t="str">
+        <v>❌ Incorrect answer for Q6.</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
       <c r="A73" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B73" t="str">
-        <v>bug_q2</v>
+        <v>v2_tech_q7</v>
       </c>
       <c r="C73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q2. Infinite Loop: x=1. WHILE x&lt;=5 PRINT x. What is the bug?
-Enter in caps</v>
-      </c>
-      <c r="D73" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q7. Which of these has the largest storage capacity?
+A. 500 KB
+B. 2 MB
+C. 1 GB
+D. 5 TB</v>
       </c>
       <c r="E73" t="str">
         <v>yes</v>
+      </c>
+      <c r="F73" t="str">
+        <v>❌ Question 7 is mandatory.</v>
+      </c>
+      <c r="G73" t="str">
+        <v>. = 'd'</v>
+      </c>
+      <c r="H73" t="str">
+        <v>❌ Incorrect answer for Q7.</v>
       </c>
     </row>
     <row r="74" xml:space="preserve">
       <c r="A74" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B74" t="str">
-        <v>bug_q3</v>
+        <v>v2_tech_q8</v>
       </c>
       <c r="C74" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q3. Swapped Variables: a=10, b=20. a=b; b=a. After execution, what are a and b?
-Enter in caps</v>
-      </c>
-      <c r="D74" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q8. Which is the correct order from smallest to largest?
+A. KB → MB → GB → TB
+B. MB → KB → TB → GB
+C. GB → MB → KB → TB
+D. TB → GB → MB → KB</v>
       </c>
       <c r="E74" t="str">
         <v>yes</v>
+      </c>
+      <c r="F74" t="str">
+        <v>❌ Question 8 is mandatory.</v>
+      </c>
+      <c r="G74" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H74" t="str">
+        <v>❌ Incorrect answer for Q8.</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
       <c r="A75" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B75" t="str">
-        <v>bug_q4</v>
+        <v>v2_tech_q9</v>
       </c>
       <c r="C75" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q4. Wrong Output: FOR i=1 TO 5 PRINT i. System displays: 1 2 3 4 6. Where is the bug?
-Enter in caps</v>
-      </c>
-      <c r="D75" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q9. A website address begins with: https://. What does the S mainly indicate?
+A. The website is a search engine
+B. The connection uses security/encryption
+C. The website is stored on your computer
+D. The website has no password</v>
       </c>
       <c r="E75" t="str">
         <v>yes</v>
+      </c>
+      <c r="F75" t="str">
+        <v>❌ Question 9 is mandatory.</v>
+      </c>
+      <c r="G75" t="str">
+        <v>. = 'b'</v>
+      </c>
+      <c r="H75" t="str">
+        <v>❌ Incorrect answer for Q9.</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
       <c r="A76" t="str">
-        <v>text</v>
+        <v>select_one mcq_opts</v>
       </c>
       <c r="B76" t="str">
-        <v>bug_q5</v>
+        <v>v2_tech_q10</v>
       </c>
       <c r="C76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q5. Password Bug: IF password="CSE123" PRINT "Access Granted" ELSE PRINT "Access Granted". Find the bug:
-Enter in caps</v>
-      </c>
-      <c r="D76" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v xml:space="preserve">Q10. You type a website address into your browser. Which sequence is the most appropriate?
+A. DNS finds the IP → Browser connects to the server → Website data is requested
+B. Browser requests the webpage → DNS shuts down → Server connects
+C. RAM finds the website → Keyboard connects to DNS → Router prints it
+D. DHCP creates the webpage → Monitor finds the IP → Browser shuts down</v>
       </c>
       <c r="E76" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="77" xml:space="preserve">
+      <c r="F76" t="str">
+        <v>❌ Question 10 is mandatory.</v>
+      </c>
+      <c r="G76" t="str">
+        <v>. = 'a'</v>
+      </c>
+      <c r="H76" t="str">
+        <v>❌ Incorrect answer for Q10.</v>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77" t="str">
-        <v>text</v>
-      </c>
-      <c r="B77" t="str">
-        <v>bug_q6</v>
-      </c>
-      <c r="C77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q6. Array Bug: [10, 20, 30, 40, 50]. Program says PRINT array[5]. What is wrong?
-Enter in caps</v>
-      </c>
-      <c r="D77" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E77" t="str">
-        <v>yes</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="78" xml:space="preserve">
       <c r="A78" t="str">
-        <v>text</v>
+        <v>image</v>
       </c>
       <c r="B78" t="str">
-        <v>bug_q7</v>
+        <v>r2_v2_cse_photo</v>
       </c>
       <c r="C78" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q7. Flowchart Bug: Start → Input number → number % 2 == 0? YES→ODD, NO→EVEN. Find the bug:
-Enter in caps</v>
+        <v xml:space="preserve">📸 Upload Photo of Team Solving Variant 2 Challenge (MANDATORY)
+Photo upload is mandatory</v>
       </c>
       <c r="D78" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>Take a clear photo of your team at the station.</v>
       </c>
       <c r="E78" t="str">
         <v>yes</v>
+      </c>
+      <c r="F78" t="str">
+        <v>❌ Station photo upload is mandatory.</v>
+      </c>
+      <c r="I78" t="str">
+        <v>${v2_bug_q1} = 'a' and ${v2_bug_q2} = 'a' and ${v2_bug_q3} = 'b' and ${v2_bug_q4} = 'b' and ${v2_bug_q5} = 'a' and ${v2_bug_q6} = 'b' and ${v2_bug_q7} = 'a' and ${v2_bug_q8} = 'a' and ${v2_bug_q9} = 'a' and ${v2_bug_q10} = 'a' and ${v2_tech_q1} = 'b' and ${v2_tech_q2} = 'a' and ${v2_tech_q3} = 'b' and ${v2_tech_q4} = 'a' and ${v2_tech_q5} = 'b' and ${v2_tech_q6} = 'b' and ${v2_tech_q7} = 'd' and ${v2_tech_q8} = 'a' and ${v2_tech_q9} = 'b' and ${v2_tech_q10} = 'a'</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
@@ -1834,11 +2187,11 @@
         <v>text</v>
       </c>
       <c r="B79" t="str">
-        <v>bug_q8</v>
+        <v>r2_v2_code</v>
       </c>
       <c r="C79" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q8. Detective Debugging: Input: 5. x=1; FOR i=1 TO x { x=x+1 }; PRINT x. Why doesn't this behave as expected?
-Enter in caps</v>
+        <v xml:space="preserve">Enter Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D79" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
@@ -1846,222 +2199,259 @@
       <c r="E79" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="80" xml:space="preserve">
+      <c r="F79" t="str">
+        <v>❌ Volunteer clearance code is mandatory.</v>
+      </c>
+      <c r="G79" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'CSE-ZUCKER-4'</v>
+      </c>
+      <c r="H79" t="str">
+        <v>❌ Incorrect code. Check the code obtained after completing the challenge.</v>
+      </c>
+      <c r="I79" t="str">
+        <v>${v2_bug_q1} = 'a' and ${v2_bug_q2} = 'a' and ${v2_bug_q3} = 'b' and ${v2_bug_q4} = 'b' and ${v2_bug_q5} = 'a' and ${v2_bug_q6} = 'b' and ${v2_bug_q7} = 'a' and ${v2_bug_q8} = 'a' and ${v2_bug_q9} = 'a' and ${v2_bug_q10} = 'a' and ${v2_tech_q1} = 'b' and ${v2_tech_q2} = 'a' and ${v2_tech_q3} = 'b' and ${v2_tech_q4} = 'a' and ${v2_tech_q5} = 'b' and ${v2_tech_q6} = 'b' and ${v2_tech_q7} = 'd' and ${v2_tech_q8} = 'a' and ${v2_tech_q9} = 'b' and ${v2_tech_q10} = 'a'</v>
+      </c>
+    </row>
+    <row r="80">
       <c r="A80" t="str">
-        <v>text</v>
-      </c>
-      <c r="B80" t="str">
-        <v>bug_q9</v>
-      </c>
-      <c r="C80" t="str" xml:space="preserve">
-        <v xml:space="preserve">Q9. Find TWO Bugs: a=5, b=10. IF a&gt;b PRINT "b is larger" ELSE PRINT "a is larger". What are the 2 bugs?
-Enter in caps</v>
-      </c>
-      <c r="D80" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E80" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="81" xml:space="preserve">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="81">
       <c r="A81" t="str">
-        <v>image</v>
-      </c>
-      <c r="B81" t="str">
-        <v>r2_v2_bug_photo</v>
-      </c>
-      <c r="C81" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Team Solving Bug Hunter
-Photo upload is mandatory</v>
-      </c>
-      <c r="D81" t="str">
-        <v>Take a clear photo of your team solving Bug Hunter.</v>
-      </c>
-      <c r="E81" t="str">
-        <v>yes</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
+      </c>
+      <c r="B82" t="str">
+        <v>r3_cyber_loc_group</v>
+      </c>
+      <c r="C82" t="str">
+        <v>ROUND 3 LOCATION CLUE</v>
+      </c>
+      <c r="I82" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != ''))</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
       <c r="A83" t="str">
+        <v>note</v>
+      </c>
+      <c r="B83" t="str">
+        <v>r3_cyber_morse_note</v>
+      </c>
+      <c r="C83" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE: MORSE CODE MESSAGE
+Decode the Morse-code message to reveal your next location.
+Morse Message:
+--. --- / - --- / -.-. -.-- -... . .-.
+Refer to the Morse key reference image attached below.
+Enter code in caps</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Decode each Morse group to discover the next location.</v>
+      </c>
+      <c r="J83" t="str">
+        <v>morse.jpeg</v>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str">
         <v>text</v>
       </c>
-      <c r="B83" t="str">
-        <v>r2_v2_code</v>
-      </c>
-      <c r="C83" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code (Variant 2)
+      <c r="B84" t="str">
+        <v>r3_cyber_loc_answer</v>
+      </c>
+      <c r="C84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter your decoded message: (MANDATORY)
 Enter code in caps</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D84" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E83" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F83" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4'</v>
-      </c>
-      <c r="G83" t="str">
-        <v>❌ Incorrect code. Enter CSE-ZUCKERBERG-4 provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="85">
+      <c r="E84" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F84" t="str">
+        <v>❌ Decoded message is mandatory.</v>
+      </c>
+      <c r="G84" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'GO TO CYBER' or normalize-space(.) = 'CYBER' or normalize-space(.) = 'CYBER BLOCK')</v>
+      </c>
+      <c r="H84" t="str">
+        <v>❌ Incorrect. Decode each Morse-code group carefully and try again.</v>
+      </c>
+      <c r="J84" t="str">
+        <v>morse.jpeg</v>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
       <c r="A85" t="str">
-        <v>end_group</v>
+        <v>note</v>
+      </c>
+      <c r="B85" t="str">
+        <v>r3_cyber_proceed_note</v>
+      </c>
+      <c r="C85" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Correct! Proceed to the location identified by the decoded message.
+Enter code in caps</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Proceed to the location for the QR hunt.</v>
+      </c>
+      <c r="I85" t="str">
+        <v>normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK'</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B86" t="str">
-        <v>r3_cyber_loc_group</v>
-      </c>
-      <c r="C86" t="str">
-        <v>ROUND 3 LOCATION CLUE</v>
-      </c>
-      <c r="H86" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != ''))</v>
-      </c>
-    </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87" t="str">
-        <v>note</v>
-      </c>
       <c r="B87" t="str">
-        <v>r3_morse_note</v>
-      </c>
-      <c r="C87" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE: MORSE CODE
-Examine the Morse code chart in the image below and decode the encrypted message to reveal your next destination!
-📜 CIPHER TEXT:
---.  ---
--  ---
--.-.  -.--  -...  .  .-.
-Enter code in caps</v>
-      </c>
-      <c r="D87" t="str">
-        <v>Decode the Morse code message using the attached image chart.</v>
+        <v>r3_cyber_qr_group</v>
+      </c>
+      <c r="C87" t="str">
+        <v>ROUND 3 — QR HUNT</v>
       </c>
       <c r="I87" t="str">
-        <v>morse.jpeg</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK')</v>
       </c>
     </row>
     <row r="88" xml:space="preserve">
       <c r="A88" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B88" t="str">
-        <v>r3_morse_answer</v>
+        <v>r3_cyber_qr_note</v>
       </c>
       <c r="C88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter decoded message:
+        <v xml:space="preserve">📍 ROUND 3: QR HUNT
+Find the designated QR code at this location and scan it. Follow the instructions provided by the QR challenge.
 Enter code in caps</v>
       </c>
       <c r="D88" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E88" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F88" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER'</v>
-      </c>
-      <c r="G88" t="str">
-        <v>❌ Incorrect decoded message. Decode the Morse code and enter in CAPS.</v>
-      </c>
-      <c r="I88" t="str">
-        <v>morse.jpeg</v>
+        <v>Locate and scan the hidden QR code.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
+        <v>barcode</v>
+      </c>
+      <c r="B89" t="str">
+        <v>r3_cyber_qr_scan</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Scan Discovered QR Code (MANDATORY)</v>
+      </c>
+      <c r="D89" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E89" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F89" t="str">
+        <v>❌ QR code scanning is mandatory.</v>
+      </c>
+      <c r="G89" t="str">
+        <v>normalize-space(.) = 'JAMES_BOND'</v>
+      </c>
+      <c r="H89" t="str">
+        <v>❌ Incorrect code. Continue the QR hunt and check the code carefully.</v>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90" t="str">
+        <v>image</v>
+      </c>
+      <c r="B90" t="str">
+        <v>r3_cyber_qr_photo</v>
+      </c>
+      <c r="C90" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Discovered QR Code / Station (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Take a clear photo of the discovered QR code location.</v>
+      </c>
+      <c r="E90" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F90" t="str">
+        <v>❌ Station photo upload is mandatory.</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="str">
+    <row r="92">
+      <c r="A92" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B90" t="str">
-        <v>cyber_arrival_group</v>
-      </c>
-      <c r="C90" t="str">
-        <v>CYBER ARRIVAL</v>
-      </c>
-      <c r="H90" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER')</v>
-      </c>
-    </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91" t="str">
+      <c r="B92" t="str">
+        <v>r4_mba_loc_group</v>
+      </c>
+      <c r="C92" t="str">
+        <v>ROUND 4 LOCATION CLUE</v>
+      </c>
+      <c r="I92" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != ''</v>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str">
         <v>note</v>
       </c>
-      <c r="B91" t="str">
-        <v>cyber_arrival_note</v>
-      </c>
-      <c r="C91" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO CYBER BLOCK
-Report immediately to the Cyber station and meet the volunteer to receive your arrival verification code.
+      <c r="B93" t="str">
+        <v>r4_mba_loc_note</v>
+      </c>
+      <c r="C93" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 4 LOCATION CLUE
+"Numbers become stories here.
+Stories become strategies.
+Strategies become presentations.
+Where managers learn to turn information into decisions,
+find me."
 Enter code in caps</v>
       </c>
-      <c r="D91" t="str">
-        <v>Meet volunteer at Cyber station.</v>
-      </c>
-    </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92" t="str">
+      <c r="D93" t="str">
+        <v>Solve the riddle to identify your next destination.</v>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94" t="str">
         <v>text</v>
       </c>
-      <c r="B92" t="str">
-        <v>r3_cyber_start_code</v>
-      </c>
-      <c r="C92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Cyber Volunteer Start Code
+      <c r="B94" t="str">
+        <v>r4_mba_loc_answer</v>
+      </c>
+      <c r="C94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter your deduced destination location: (MANDATORY)
 Enter code in caps</v>
       </c>
-      <c r="D92" t="str">
+      <c r="D94" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E92" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F92" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF'</v>
-      </c>
-      <c r="G92" t="str">
-        <v>❌ Incorrect code. Enter CYBER-THIEF in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B94" t="str">
-        <v>r3_cy_qr_group</v>
-      </c>
-      <c r="C94" t="str">
-        <v>ROUND 3 — QR HUNT</v>
+      <c r="E94" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F94" t="str">
+        <v>❌ Destination location is mandatory.</v>
+      </c>
+      <c r="G94" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MBA' or normalize-space(.) = 'MBA BLOCK')</v>
       </c>
       <c r="H94" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF'</v>
+        <v>❌ Not quite. Reconsider each of the three clues and how they connect.</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -2069,27 +2459,29 @@
         <v>note</v>
       </c>
       <c r="B95" t="str">
-        <v>r3_cy_qr_note</v>
+        <v>r4_mba_proceed_note</v>
       </c>
       <c r="C95" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3: QR HUNT
-Search the location physically to locate the hidden QR code.
-Scan the QR code using the scanner below.
+        <v xml:space="preserve">🏃 Correct! Proceed to the location identified by your answer and look for the physical challenge.
 Enter code in caps</v>
       </c>
       <c r="D95" t="str">
-        <v>Locate and scan the hidden QR code.</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>Proceed to the location and ask volunteer for start code.</v>
+      </c>
+      <c r="I95" t="str">
+        <v>normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK'</v>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
-        <v>barcode</v>
+        <v>text</v>
       </c>
       <c r="B96" t="str">
-        <v>r3_cy_qr_scan</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Scan Discovered QR Code</v>
+        <v>r4_mba_start_code</v>
+      </c>
+      <c r="C96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D96" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
@@ -2098,398 +2490,352 @@
         <v>yes</v>
       </c>
       <c r="F96" t="str">
-        <v>normalize-space(.) = 'JAMES_BOND' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND'</v>
+        <v>❌ START CODE is mandatory.</v>
       </c>
       <c r="G96" t="str">
-        <v>❌ Incorrect QR code scanned. Search for the correct QR code at this station.</v>
-      </c>
-    </row>
-    <row r="97" xml:space="preserve">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'MONEY_BROTHA' or normalize-space(.) = 'MONEY-BROTHA')</v>
+      </c>
+      <c r="H96" t="str">
+        <v>❌ Incorrect START CODE. Enter MONEY_BROTHA in CAPS provided by the volunteer.</v>
+      </c>
+      <c r="I96" t="str">
+        <v>normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK'</v>
+      </c>
+    </row>
+    <row r="97">
       <c r="A97" t="str">
-        <v>image</v>
-      </c>
-      <c r="B97" t="str">
-        <v>r3_cy_qr_photo</v>
-      </c>
-      <c r="C97" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered QR Code / Station
-Photo upload is mandatory</v>
-      </c>
-      <c r="D97" t="str">
-        <v>Take a clear photo of the discovered QR code location.</v>
-      </c>
-      <c r="E97" t="str">
-        <v>yes</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B98" t="str">
+        <v>r4_mba_phy_group</v>
+      </c>
+      <c r="C98" t="str">
+        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
+      </c>
+      <c r="I98" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA')</v>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str">
+        <v>note</v>
+      </c>
+      <c r="B99" t="str">
+        <v>r4_mba_phy_note</v>
+      </c>
+      <c r="C99" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE
+Report to the station and complete the physical challenge under volunteer supervision.
+Enter code in caps</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Complete physical challenge with volunteer.</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>select_one challenge_status_list</v>
+      </c>
+      <c r="B100" t="str">
+        <v>r4_mba_status</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Challenge Status (MANDATORY)</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Select PASSED once completed with volunteer.</v>
+      </c>
+      <c r="E100" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F100" t="str">
+        <v>❌ Challenge status selection is mandatory.</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>note</v>
+      </c>
+      <c r="B101" t="str">
+        <v>r4_mba_not_passed_note</v>
+      </c>
+      <c r="C101" t="str">
+        <v>⚠️ Please follow the organizer's instructions before continuing.</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Complete the physical challenge as instructed.</v>
+      </c>
+      <c r="I101" t="str">
+        <v>${r4_mba_status} = 'not_passed'</v>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str">
+        <v>image</v>
+      </c>
+      <c r="B102" t="str">
+        <v>r4_mba_phy_photo</v>
+      </c>
+      <c r="C102" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Take a clear photo of your team completing the physical challenge.</v>
+      </c>
+      <c r="E102" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F102" t="str">
+        <v>❌ Challenge photo upload is mandatory.</v>
+      </c>
+      <c r="I102" t="str">
+        <v>${r4_mba_status} = 'passed'</v>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str">
+        <v>text</v>
+      </c>
+      <c r="B103" t="str">
+        <v>r4_mba_phy_code</v>
+      </c>
+      <c r="C103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer Completion Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D103" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E103" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F103" t="str">
+        <v>❌ Volunteer completion code is mandatory.</v>
+      </c>
+      <c r="G103" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'RAVI-KISHEN' or normalize-space(.) = 'RAVI_KISHEN')</v>
+      </c>
+      <c r="H103" t="str">
+        <v>❌ Incorrect code. Enter RAVI-KISHEN in CAPS provided by the volunteer.</v>
+      </c>
+      <c r="I103" t="str">
+        <v>${r4_mba_status} = 'passed'</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="str">
+    <row r="105">
+      <c r="A105" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B99" t="str">
-        <v>r4_mba_loc_group</v>
-      </c>
-      <c r="C99" t="str">
-        <v>ROUND 4 LOCATION CLUE</v>
-      </c>
-      <c r="H99" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != ''</v>
-      </c>
-    </row>
-    <row r="100" xml:space="preserve">
-      <c r="A100" t="str">
+      <c r="B105" t="str">
+        <v>final_puzzles_group</v>
+      </c>
+      <c r="C105" t="str">
+        <v>FINAL ROUND</v>
+      </c>
+      <c r="I105" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA') and ${r4_mba_status} = 'passed' and (normalize-space(${r4_mba_phy_code}) = 'RAVI-KISHEN' or normalize-space(${r4_mba_phy_code}) = 'RAVI_KISHEN') and ${r4_mba_phy_photo} != ''</v>
+      </c>
+    </row>
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str">
         <v>note</v>
       </c>
-      <c r="B100" t="str">
-        <v>r4_mba_loc_note</v>
-      </c>
-      <c r="C100" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 4 LOCATION CLUE: THREE STEPS
-Follow the three clues to identify the next campus destination:
-1. The one who gives wisdom
-2. Look below
-3. Where students prepare for their next career step
+      <c r="B106" t="str">
+        <v>final_audi_stage_intro</v>
+      </c>
+      <c r="C106" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏛️ FINAL ROUND — RIDDLES
+Solve the two final riddles to reveal the final destination!
 Enter code in caps</v>
       </c>
-      <c r="D100" t="str">
-        <v>Follow the 3 clues to deduce the destination block.</v>
-      </c>
-    </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str">
+      <c r="D106" t="str">
+        <v>Solve the final riddles in CAPS.</v>
+      </c>
+    </row>
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str">
         <v>text</v>
       </c>
-      <c r="B101" t="str">
-        <v>r4_mba_loc_answer</v>
-      </c>
-      <c r="C101" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter destination location
+      <c r="B107" t="str">
+        <v>final_riddle1_answer</v>
+      </c>
+      <c r="C107" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧩 AUDITORIUM RIDDLE: (MANDATORY)
+"I am empty, yet I am built for crowds.
+I have a stage, but no actors of my own.
+I have countless seats, but none are meant to sleep.
+When a voice rises before me, silence falls behind me.
+When the lights awaken, all eyes face one direction.
+What am I?"
 Enter code in caps</v>
       </c>
-      <c r="D101" t="str">
+      <c r="D107" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E101" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F101" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK'</v>
-      </c>
-      <c r="G101" t="str">
-        <v>❌ Incorrect destination. Follow the clues and enter the block in CAPS.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B103" t="str">
-        <v>mba_arrival_group</v>
-      </c>
-      <c r="C103" t="str">
-        <v>MBA ARRIVAL</v>
-      </c>
-      <c r="H103" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK')</v>
-      </c>
-    </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str">
-        <v>note</v>
-      </c>
-      <c r="B104" t="str">
-        <v>mba_arrival_note</v>
-      </c>
-      <c r="C104" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏃 PROCEED TO MBA BLOCK
-Report immediately to the MBA station and meet the volunteer to receive your arrival verification code.
-Enter code in caps</v>
-      </c>
-      <c r="D104" t="str">
-        <v>Meet volunteer at MBA station.</v>
-      </c>
-    </row>
-    <row r="105" xml:space="preserve">
-      <c r="A105" t="str">
-        <v>text</v>
-      </c>
-      <c r="B105" t="str">
-        <v>r4_mba_start_code</v>
-      </c>
-      <c r="C105" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter MBA Volunteer Arrival Code
-Enter code in caps</v>
-      </c>
-      <c r="D105" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E105" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F105" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA'</v>
-      </c>
-      <c r="G105" t="str">
-        <v>❌ Incorrect code. Enter MONEY-BROTHA in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B107" t="str">
-        <v>r4_mba_phy_group</v>
-      </c>
-      <c r="C107" t="str">
-        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
+      <c r="E107" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F107" t="str">
+        <v>❌ Solving Riddle 1 is mandatory.</v>
+      </c>
+      <c r="G107" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'AUDITORIUM' or normalize-space(.) = 'AUDI')</v>
       </c>
       <c r="H107" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and translate(normalize-space(${r4_mba_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA'</v>
+        <v>❌ Incorrect answer. Solve Riddle 1 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
       <c r="A108" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B108" t="str">
-        <v>r4_mba_phy_note</v>
+        <v>final_riddle2_stage_answer</v>
       </c>
       <c r="C108" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE (COLOURED CUPS)
-Report to the MBA station and complete the 7 coloured paper cups physical coordination challenge under volunteer supervision.
+        <v xml:space="preserve">🎭 STAGE RIDDLE: (MANDATORY)
+"I am elevated above the crowd, where performers stand and spotlights shine.
+Underneath my wooden floor or behind the curtains, the ultimate secret waits.
+What am I?"
 Enter code in caps</v>
       </c>
       <c r="D108" t="str">
-        <v>Complete physical challenge with volunteer.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E108" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F108" t="str">
+        <v>❌ Solving Riddle 2 is mandatory.</v>
+      </c>
+      <c r="G108" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'STAGE'</v>
+      </c>
+      <c r="H108" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I108" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA') and ${r4_mba_status} = 'passed' and (normalize-space(${r4_mba_phy_code}) = 'RAVI-KISHEN' or normalize-space(${r4_mba_phy_code}) = 'RAVI_KISHEN') and ${r4_mba_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
       </c>
     </row>
     <row r="109" xml:space="preserve">
       <c r="A109" t="str">
-        <v>image</v>
+        <v>note</v>
       </c>
       <c r="B109" t="str">
-        <v>r4_mba_phy_photo</v>
+        <v>final_proceed_stage_note</v>
       </c>
       <c r="C109" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion
-Photo upload is mandatory</v>
+        <v xml:space="preserve">🏃 Proceed to the final location identified!
+Solve the final puzzle at the stage, upload a photo of the completed puzzle, and get your clearance code from the Chief Judge!
+Enter code in caps</v>
       </c>
       <c r="D109" t="str">
-        <v>Take a clear photo of your team completing the physical challenge.</v>
-      </c>
-      <c r="E109" t="str">
-        <v>yes</v>
+        <v>Go to the stage to solve the final puzzle.</v>
+      </c>
+      <c r="I109" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA') and ${r4_mba_status} = 'passed' and (normalize-space(${r4_mba_phy_code}) = 'RAVI-KISHEN' or normalize-space(${r4_mba_phy_code}) = 'RAVI_KISHEN') and ${r4_mba_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
       </c>
     </row>
     <row r="110" xml:space="preserve">
       <c r="A110" t="str">
+        <v>image</v>
+      </c>
+      <c r="B110" t="str">
+        <v>final_solved_puzzle_photo</v>
+      </c>
+      <c r="C110" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Take a clear photo of your team's completed/solved puzzle.</v>
+      </c>
+      <c r="E110" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F110" t="str">
+        <v>❌ Photo of the solved puzzle is mandatory.</v>
+      </c>
+      <c r="I110" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA') and ${r4_mba_status} = 'passed' and (normalize-space(${r4_mba_phy_code}) = 'RAVI-KISHEN' or normalize-space(${r4_mba_phy_code}) = 'RAVI_KISHEN') and ${r4_mba_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str">
         <v>text</v>
       </c>
-      <c r="B110" t="str">
-        <v>r4_mba_phy_code</v>
-      </c>
-      <c r="C110" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code
+      <c r="B111" t="str">
+        <v>final_stage_volunteer_code</v>
+      </c>
+      <c r="C111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Final Volunteer Clearance Code (MANDATORY)
 Enter code in caps</v>
       </c>
-      <c r="D110" t="str">
+      <c r="D111" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
-      <c r="E110" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F110" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RAVI-KISHEN'</v>
-      </c>
-      <c r="G110" t="str">
-        <v>❌ Incorrect code. Enter RAVI-KISHEN in CAPS provided by the volunteer.</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="112">
+      <c r="E111" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F111" t="str">
+        <v>❌ Final clearance code is mandatory.</v>
+      </c>
+      <c r="G111" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'FINAL-PATH4' or normalize-space(.) = 'FINAL-PATH1' or normalize-space(.) = 'FINAL-PATH2' or normalize-space(.) = 'FINAL-PATH3')</v>
+      </c>
+      <c r="H111" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
+      </c>
+      <c r="I111" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA') and ${r4_mba_status} = 'passed' and (normalize-space(${r4_mba_phy_code}) = 'RAVI-KISHEN' or normalize-space(${r4_mba_phy_code}) = 'RAVI_KISHEN') and ${r4_mba_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="112" xml:space="preserve">
       <c r="A112" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B112" t="str">
-        <v>final_puzzles_group</v>
-      </c>
-      <c r="C112" t="str">
-        <v>FINAL PUZZLES</v>
-      </c>
-      <c r="H112" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and translate(normalize-space(${r4_mba_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA' and translate(normalize-space(${r4_mba_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RAVI-KISHEN' and ${r4_mba_phy_photo} != ''</v>
-      </c>
-    </row>
-    <row r="113" xml:space="preserve">
+        <v>final_congratulations_screen</v>
+      </c>
+      <c r="C112" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎉 CONGRATULATIONS! YOU HAVE COMPLETED PATH 4!
+🏆 You have successfully entered the final clearance code!
+🔔 NOW RUN TO GO RING THE BELL TO WIN THE GAME! 🔔🏃💨</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Run to ring the bell to claim victory!</v>
+      </c>
+      <c r="I112" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_canteen_code}) = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and ${r2_math_answer} = 9 and normalize-space(${r2_cse_start_code}) = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and normalize-space(${r2_v1_code}) = 'CSE-EINSTEIN-4' and ${r2_v1_cse_photo} != '') or (${r2_cse_variant_select} = 'var2' and normalize-space(${r2_v2_code}) = 'CSE-ZUCKER-4' and ${r2_v2_cse_photo} != '')) and (normalize-space(${r3_cyber_loc_answer}) = 'GO TO CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER' or normalize-space(${r3_cyber_loc_answer}) = 'CYBER BLOCK') and normalize-space(${r3_cyber_qr_scan}) = 'JAMES_BOND' and ${r3_cyber_qr_photo} != '' and (normalize-space(${r4_mba_loc_answer}) = 'MBA' or normalize-space(${r4_mba_loc_answer}) = 'MBA BLOCK') and (normalize-space(${r4_mba_start_code}) = 'MONEY_BROTHA' or normalize-space(${r4_mba_start_code}) = 'MONEY-BROTHA') and ${r4_mba_status} = 'passed' and (normalize-space(${r4_mba_phy_code}) = 'RAVI-KISHEN' or normalize-space(${r4_mba_phy_code}) = 'RAVI_KISHEN') and ${r4_mba_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH4' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH3') and ${final_solved_puzzle_photo} != ''</v>
+      </c>
+    </row>
+    <row r="113">
       <c r="A113" t="str">
-        <v>note</v>
-      </c>
-      <c r="B113" t="str">
-        <v>final_audi_stage_intro</v>
-      </c>
-      <c r="C113" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏛️ FINAL CHALLENGES
-Proceed to the location and solve the two final riddles!
-Enter code in caps</v>
-      </c>
-      <c r="D113" t="str">
-        <v>Solve the final riddles.</v>
-      </c>
-    </row>
-    <row r="114" xml:space="preserve">
-      <c r="A114" t="str">
-        <v>text</v>
-      </c>
-      <c r="B114" t="str">
-        <v>final_riddle1_answer</v>
-      </c>
-      <c r="C114" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧩 RIDDLE 1:
-"I am a place of darkness until the lights ignite. I hold hundreds of red seats, host grand orientations, and echo with voices through microphones. Where are you standing?"
-Enter code in caps</v>
-      </c>
-      <c r="D114" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E114" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F114" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI'</v>
-      </c>
-      <c r="G114" t="str">
-        <v>❌ Incorrect answer. Solve the riddle and enter in CAPS.</v>
-      </c>
-    </row>
-    <row r="115" xml:space="preserve">
-      <c r="A115" t="str">
-        <v>text</v>
-      </c>
-      <c r="B115" t="str">
-        <v>final_riddle2_stage_answer</v>
-      </c>
-      <c r="C115" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎭 RIDDLE 2:
-"I am elevated above the crowd, where performers stand and spotlights shine. Underneath my wooden floor or behind the curtains, the ultimate secret waits. What am I?"
-Enter code in caps</v>
-      </c>
-      <c r="D115" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E115" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F115" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
-      </c>
-      <c r="G115" t="str">
-        <v>❌ Incorrect answer. Solve the stage riddle and enter in CAPS.</v>
-      </c>
-      <c r="H115" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and translate(normalize-space(${r4_mba_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA' and translate(normalize-space(${r4_mba_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RAVI-KISHEN' and ${r4_mba_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI')</v>
-      </c>
-    </row>
-    <row r="116" xml:space="preserve">
-      <c r="A116" t="str">
-        <v>image</v>
-      </c>
-      <c r="B116" t="str">
-        <v>final_solved_puzzle_photo</v>
-      </c>
-      <c r="C116" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle
-Photo upload is mandatory</v>
-      </c>
-      <c r="D116" t="str">
-        <v>Take a clear photo of your team's completed/solved puzzle.</v>
-      </c>
-      <c r="E116" t="str">
-        <v>yes</v>
-      </c>
-      <c r="H116" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and translate(normalize-space(${r4_mba_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA' and translate(normalize-space(${r4_mba_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RAVI-KISHEN' and ${r4_mba_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
-      </c>
-    </row>
-    <row r="117" xml:space="preserve">
-      <c r="A117" t="str">
-        <v>text</v>
-      </c>
-      <c r="B117" t="str">
-        <v>final_stage_volunteer_code</v>
-      </c>
-      <c r="C117" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Final Volunteer Clearance Code
-Enter code in caps</v>
-      </c>
-      <c r="D117" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E117" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F117" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH4' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH2' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH3'</v>
-      </c>
-      <c r="G117" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the Chief Judge.</v>
-      </c>
-      <c r="H117" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and translate(normalize-space(${r4_mba_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA' and translate(normalize-space(${r4_mba_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RAVI-KISHEN' and ${r4_mba_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
-      </c>
-    </row>
-    <row r="118" xml:space="preserve">
-      <c r="A118" t="str">
-        <v>note</v>
-      </c>
-      <c r="B118" t="str">
-        <v>final_congratulations_screen</v>
-      </c>
-      <c r="C118" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎉 CONGRATULATIONS! PATH 4 COMPLETED.
-🏆 You have successfully conquered every challenge, puzzle, and cipher on PATH 4!
-Show this completion screen immediately to the Chief Judge to lock in your finishing timestamp and rank!</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Report to Chief Judge to finalize completion.</v>
-      </c>
-      <c r="H118" t="str">
-        <v>${team_name} != '' and ${team_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_canteen_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MEOW-BOW-4' and ${r1_canteen_photo} != '' and (normalize-space(${r2_math_answer}) = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = '9' or translate(normalize-space(${r2_math_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NINE') and (translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE' or translate(normalize-space(${r2_cse_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE BLOCK') and translate(normalize-space(${r2_cse_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-START' and ((${r2_cse_variant_select} = 'var1' and translate(normalize-space(${r2_v1_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-EINSTEIN-4' and ${r2_v1_algo_photo} != '' and ${r2_v1_binary_photo} != '') or (${r2_cse_variant_select} = 'var2' and (translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKERBERG-4' or translate(normalize-space(${r2_v2_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CSE-ZUCKER-4') and ${r2_v2_pattern_photo} != '' and ${r2_v2_bug_photo} != '')) and (translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GO TO CYBER' or translate(normalize-space(${r3_morse_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER') and translate(normalize-space(${r3_cyber_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CYBER-THIEF' and (normalize-space(${r3_cy_qr_scan}) = 'JAMES_BOND' or translate(normalize-space(${r3_cy_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JAMES_BOND') and ${r3_cy_qr_photo} != '' and (translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r4_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and translate(normalize-space(${r4_mba_start_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONEY-BROTHA' and translate(normalize-space(${r4_mba_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RAVI-KISHEN' and ${r4_mba_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE' and (translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH4' or translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1' or translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH2' or translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH3') and ${final_solved_puzzle_photo} != ''</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
         <v>end_group</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J113"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2510,7 +2856,7 @@
         <v>var1</v>
       </c>
       <c r="C2" t="str">
-        <v>Variant 1: Algo Relay + Binary Breaker</v>
+        <v>Variant A: Logical Challenge 1 (Algo Relay + Cyber Detective)</v>
       </c>
     </row>
     <row r="3">
@@ -2521,12 +2867,78 @@
         <v>var2</v>
       </c>
       <c r="C3" t="str">
-        <v>Variant 2: Pattern Hack + Bug Hunter</v>
+        <v>Variant B: Logical Challenge 2 (Bug Hunter + Tech Detective)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>mcq_opts</v>
+      </c>
+      <c r="B4" t="str">
+        <v>a</v>
+      </c>
+      <c r="C4" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>mcq_opts</v>
+      </c>
+      <c r="B5" t="str">
+        <v>b</v>
+      </c>
+      <c r="C5" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>mcq_opts</v>
+      </c>
+      <c r="B6" t="str">
+        <v>c</v>
+      </c>
+      <c r="C6" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>mcq_opts</v>
+      </c>
+      <c r="B7" t="str">
+        <v>d</v>
+      </c>
+      <c r="C7" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>challenge_status_list</v>
+      </c>
+      <c r="B8" t="str">
+        <v>passed</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>challenge_status_list</v>
+      </c>
+      <c r="B9" t="str">
+        <v>not_passed</v>
+      </c>
+      <c r="C9" t="str">
+        <v>NOT PASSED</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2554,10 +2966,10 @@
         <v>FINAL CLUE — PATH 4</v>
       </c>
       <c r="B2" t="str">
-        <v>final_clue_path4</v>
+        <v>PATH4_TREASURE_HUNT</v>
       </c>
       <c r="C2" t="str">
-        <v>20260902</v>
+        <v>20260904</v>
       </c>
       <c r="D2" t="str">
         <v>default</v>

--- a/ROUTE_4_PATH4_OLD_CANTEEN_CSE_CY_MBA_AUDI/PATH4_FINAL_ODK.xlsx
+++ b/ROUTE_4_PATH4_OLD_CANTEEN_CSE_CY_MBA_AUDI/PATH4_FINAL_ODK.xlsx
@@ -483,7 +483,8 @@
 * Next 15 teams proceed to Round 3.
 * Next 7 teams proceed to Round 4.
 * Next 2 teams proceed to Round 5.
-⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+⚠️ STRICT PROGRESSION &amp; MANDATORY RULES:
+• Read each question properly as you cannot come back to the question once you go ahead!
 • Every single question, photo upload, and code entry is strictly MANDATORY.
 • All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
 • Lowercase letters will be rejected by validation.</v>
@@ -504,7 +505,7 @@
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E4" t="str">
         <v>yes</v>
@@ -531,7 +532,7 @@
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E5" t="str">
         <v>yes</v>
@@ -639,7 +640,7 @@
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E11" t="str">
         <v>yes</v>
@@ -750,7 +751,7 @@
 Enter code in caps</v>
       </c>
       <c r="D17" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E17" t="str">
         <v>yes</v>
@@ -1480,7 +1481,7 @@
 Enter code in caps</v>
       </c>
       <c r="D49" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E49" t="str">
         <v>yes</v>
@@ -2194,7 +2195,7 @@
 Enter code in caps</v>
       </c>
       <c r="D79" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E79" t="str">
         <v>yes</v>
@@ -2270,7 +2271,7 @@
 Enter code in caps</v>
       </c>
       <c r="D84" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E84" t="str">
         <v>yes</v>
@@ -2352,7 +2353,7 @@
         <v>Scan Discovered QR Code (MANDATORY)</v>
       </c>
       <c r="D89" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E89" t="str">
         <v>yes</v>
@@ -2439,7 +2440,7 @@
 Enter code in caps</v>
       </c>
       <c r="D94" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E94" t="str">
         <v>yes</v>
@@ -2484,7 +2485,7 @@
 Enter code in caps</v>
       </c>
       <c r="D96" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E96" t="str">
         <v>yes</v>
@@ -2610,7 +2611,7 @@
 Enter code in caps</v>
       </c>
       <c r="D103" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E103" t="str">
         <v>yes</v>
@@ -2681,7 +2682,7 @@
 Enter code in caps</v>
       </c>
       <c r="D107" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E107" t="str">
         <v>yes</v>
@@ -2711,7 +2712,7 @@
 Enter code in caps</v>
       </c>
       <c r="D108" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E108" t="str">
         <v>yes</v>
@@ -2784,7 +2785,7 @@
 Enter code in caps</v>
       </c>
       <c r="D111" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E111" t="str">
         <v>yes</v>
